--- a/artfynd/A 30320-2026 artfynd.xlsx
+++ b/artfynd/A 30320-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135468424</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135468425</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,8 +1034,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135468428</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30320-2026 artfynd.xlsx
+++ b/artfynd/A 30320-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135468424</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135468425</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>135468428</v>
       </c>
       <c r="B4" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30320-2026 artfynd.xlsx
+++ b/artfynd/A 30320-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135468424</v>
       </c>
       <c r="B2" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135468425</v>
       </c>
       <c r="B3" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>135468428</v>
       </c>
       <c r="B4" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30320-2026 artfynd.xlsx
+++ b/artfynd/A 30320-2026 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>135468428</v>
       </c>
       <c r="B4" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30320-2026 artfynd.xlsx
+++ b/artfynd/A 30320-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -916,53 +916,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135468428</v>
+        <v>136040191</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>96595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fredriksdal, Fredriksdal, Ög</t>
+          <t>Fredriksdal, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558081</v>
+        <v>558113</v>
       </c>
       <c r="R4" t="n">
-        <v>6430682</v>
+        <v>6430749</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,27 +981,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:21</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1 blommande, 10 bladrosetter</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,25 +995,1307 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnea Druid, Henrik Druid</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136040191</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136040349</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92278</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3008</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Timmerticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Amyloporia sinuosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fredriksdal, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>558118</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6430733</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136040349</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136042696</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92085</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fredriksdal, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>558088</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6430586</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136042696</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136043472</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92085</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fredriksdal, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>557923</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6430664</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136043472</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136040303</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91423</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fredriksdal, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>558113</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6430749</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136040303</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136043436</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92741</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fredriksdal, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>557923</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6430664</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136043436</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136043265</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80062</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fredriksdal, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>557852</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6430699</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136043265</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136040736</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57979</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fredriksdal, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>558078</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6430683</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136040736</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136043716</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57979</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fredriksdal, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>558046</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6430557</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136043716</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136042346</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5498</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fredriksdal, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>557998</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6430568</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136042346</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136043932</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58846</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fredriksdal, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>558092</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6430618</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136043932</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135468428</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fredriksdal, Fredriksdal, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>558081</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6430682</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1 blommande, 10 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Linnea Druid</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Linnea Druid, Henrik Druid</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135468428</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136043853</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99292</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fredriksdal, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>558081</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6430606</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136043853</t>
         </is>
       </c>
     </row>
@@ -1045,6 +2304,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30320-2026 artfynd.xlsx
+++ b/artfynd/A 30320-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1324,48 +1324,51 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136040303</v>
+        <v>136076669</v>
       </c>
       <c r="B8" t="n">
-        <v>91423</v>
+        <v>92085</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5685</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fredriksdal, Ög</t>
+          <t>Fredriksdal/Björkern, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558113</v>
+        <v>557990</v>
       </c>
       <c r="R8" t="n">
-        <v>6430749</v>
+        <v>6430595</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1403,71 +1406,75 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136040303</t>
+          <t>https://artportalen.se/Sighting/136076669</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136043436</v>
+        <v>136076792</v>
       </c>
       <c r="B9" t="n">
-        <v>92741</v>
+        <v>92085</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fredriksdal, Ög</t>
+          <t>Fredriksdal/Björkern, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557923</v>
+        <v>557971</v>
       </c>
       <c r="R9" t="n">
-        <v>6430664</v>
+        <v>6430606</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1505,55 +1512,56 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136043436</t>
+          <t>https://artportalen.se/Sighting/136076792</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136043265</v>
+        <v>136040303</v>
       </c>
       <c r="B10" t="n">
-        <v>80062</v>
+        <v>91423</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>5685</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557852</v>
+        <v>558113</v>
       </c>
       <c r="R10" t="n">
-        <v>6430699</v>
+        <v>6430749</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,16 +1632,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136043265</t>
+          <t>https://artportalen.se/Sighting/136040303</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136040736</v>
+        <v>136043436</v>
       </c>
       <c r="B11" t="n">
-        <v>57979</v>
+        <v>92741</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,42 +1649,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fredriksdal, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558078</v>
+        <v>557923</v>
       </c>
       <c r="R11" t="n">
-        <v>6430683</v>
+        <v>6430664</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,59 +1734,51 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136040736</t>
+          <t>https://artportalen.se/Sighting/136043436</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136043716</v>
+        <v>136043265</v>
       </c>
       <c r="B12" t="n">
-        <v>57979</v>
+        <v>80062</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fredriksdal, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558046</v>
+        <v>557852</v>
       </c>
       <c r="R12" t="n">
-        <v>6430557</v>
+        <v>6430699</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,16 +1836,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136043716</t>
+          <t>https://artportalen.se/Sighting/136043265</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136042346</v>
+        <v>136076459</v>
       </c>
       <c r="B13" t="n">
-        <v>5498</v>
+        <v>57995</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1861,46 +1853,45 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101410</v>
+        <v>100048</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fredriksdal, Ög</t>
+          <t>Fredriksdal/Björkern, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557998</v>
+        <v>558122</v>
       </c>
       <c r="R13" t="n">
-        <v>6430568</v>
+        <v>6430663</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,40 +1923,44 @@
           <t>2026-08-21</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Bohål i gammal asp</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136042346</t>
+          <t>https://artportalen.se/Sighting/136076459</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136043932</v>
+        <v>136040736</v>
       </c>
       <c r="B14" t="n">
-        <v>58846</v>
+        <v>57979</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1973,34 +1968,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208249</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fredriksdal, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558092</v>
+        <v>558078</v>
       </c>
       <c r="R14" t="n">
-        <v>6430618</v>
+        <v>6430683</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,59 +2061,59 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136043932</t>
+          <t>https://artportalen.se/Sighting/136040736</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135468428</v>
+        <v>136043716</v>
       </c>
       <c r="B15" t="n">
-        <v>99276</v>
+        <v>57979</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fredriksdal, Fredriksdal, Ög</t>
+          <t>Fredriksdal, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558081</v>
+        <v>558046</v>
       </c>
       <c r="R15" t="n">
-        <v>6430682</v>
+        <v>6430557</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,27 +2140,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:21</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>1 blommande, 10 bladrosetter</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2166,81 +2154,79 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linnea Druid, Henrik Druid</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135468428</t>
+          <t>https://artportalen.se/Sighting/136043716</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136043853</v>
+        <v>136076464</v>
       </c>
       <c r="B16" t="n">
-        <v>99292</v>
+        <v>57979</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fredriksdal, Ög</t>
+          <t>Fredriksdal/Björkern, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558081</v>
+        <v>558122</v>
       </c>
       <c r="R16" t="n">
-        <v>6430606</v>
+        <v>6430663</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2272,11 +2258,16 @@
           <t>2026-08-21</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Bohål i gammal asp</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG16" t="b">
         <v>0</v>
@@ -2284,16 +2275,1488 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136076464</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136076632</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57979</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fredriskdal/Björkern, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>558056</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6430532</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gamla hackspår på flera döda tallar. Fågeln hörts en bit bort.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136076632</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136076737</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57979</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fredriksdal/Björkern, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>558001</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6430557</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hackspår från födosök på tall</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136076737</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136076810</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57979</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Fredriksdal/Björkern, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>557982</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6430645</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gammalt, dött träd med sju bohål i spillkråkestorlek.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136076810</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136042346</v>
+      </c>
+      <c r="B20" t="n">
+        <v>5498</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fredriksdal, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>557998</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6430568</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136042346</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136076515</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5498</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fredriksdal/Björkern, Ög</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>558085</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6430572</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136076515</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136076717</v>
+      </c>
+      <c r="B22" t="n">
+        <v>5498</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Fredriksdal/Björkern, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>558001</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6430557</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136076717</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136076901</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58143</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Fredriksdal/Björkern, Ög</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>557944</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6430672</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Hört ihållande sång från tre individer på flera ställen i närheten,</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136076901</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136076908</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58138</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>fred, Ög</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>557941</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6430693</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hört ihållande sång från minst två individer på flera ställen i närheten,</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136076908</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136076497</v>
+      </c>
+      <c r="B25" t="n">
+        <v>61538</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>106670</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svart skogssnigel</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Arion ater ater</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Fredriksdal/Björkern, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>558073</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6430626</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136076497</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136076819</v>
+      </c>
+      <c r="B26" t="n">
+        <v>56713</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Fredriksdal/Björkern, Ög</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>557973</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6430659</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136076819</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136043932</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58846</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Fredriksdal, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>558092</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6430618</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136043932</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135468428</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Fredriksdal, Fredriksdal, Ög</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>558081</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6430682</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>1 blommande, 10 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Linnea Druid</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Linnea Druid, Henrik Druid</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135468428</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136043853</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99292</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Fredriksdal, Ög</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>558081</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6430606</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136043853</t>
         </is>
@@ -2316,6 +3779,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30320-2026 artfynd.xlsx
+++ b/artfynd/A 30320-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135468424</v>
       </c>
       <c r="B2" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135468425</v>
       </c>
       <c r="B3" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>136040191</v>
       </c>
       <c r="B4" t="n">
-        <v>96595</v>
+        <v>96596</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136043436</v>
       </c>
       <c r="B11" t="n">
-        <v>92741</v>
+        <v>92742</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>135468428</v>
       </c>
       <c r="B28" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>136043853</v>
       </c>
       <c r="B29" t="n">
-        <v>99292</v>
+        <v>99293</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 30320-2026 artfynd.xlsx
+++ b/artfynd/A 30320-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ29"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -916,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136040191</v>
+        <v>136104297</v>
       </c>
       <c r="B4" t="n">
-        <v>96596</v>
+        <v>96878</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,37 +927,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fredriksdal, Ög</t>
+          <t>Fredriksdal/Björkern, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558113</v>
+        <v>557986</v>
       </c>
       <c r="R4" t="n">
-        <v>6430749</v>
+        <v>6430633</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,33 +999,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136040191</t>
+          <t>https://artportalen.se/Sighting/136104297</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136040349</v>
+        <v>136040191</v>
       </c>
       <c r="B5" t="n">
-        <v>92278</v>
+        <v>96596</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,21 +1034,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3008</v>
+        <v>2671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Timmerticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Amyloporia sinuosa</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Rajchenb. &amp; al.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1053,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558118</v>
+        <v>558113</v>
       </c>
       <c r="R5" t="n">
-        <v>6430733</v>
+        <v>6430749</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,38 +1119,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136040349</t>
+          <t>https://artportalen.se/Sighting/136040191</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136042696</v>
+        <v>136040349</v>
       </c>
       <c r="B6" t="n">
-        <v>92085</v>
+        <v>92278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>3008</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1155,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558088</v>
+        <v>558118</v>
       </c>
       <c r="R6" t="n">
-        <v>6430586</v>
+        <v>6430733</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,13 +1221,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136042696</t>
+          <t>https://artportalen.se/Sighting/136040349</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136043472</v>
+        <v>136042696</v>
       </c>
       <c r="B7" t="n">
         <v>92085</v>
@@ -1257,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557923</v>
+        <v>558088</v>
       </c>
       <c r="R7" t="n">
-        <v>6430664</v>
+        <v>6430586</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,13 +1323,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136043472</t>
+          <t>https://artportalen.se/Sighting/136042696</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136076669</v>
+        <v>136043472</v>
       </c>
       <c r="B8" t="n">
         <v>92085</v>
@@ -1353,22 +1358,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fredriksdal/Björkern, Ög</t>
+          <t>Fredriksdal, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557990</v>
+        <v>557923</v>
       </c>
       <c r="R8" t="n">
-        <v>6430595</v>
+        <v>6430664</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,31 +1408,30 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Madeleine Askelöf</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Madeleine Askelöf</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136076669</t>
+          <t>https://artportalen.se/Sighting/136043472</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136076792</v>
+        <v>136076669</v>
       </c>
       <c r="B9" t="n">
         <v>92085</v>
@@ -1468,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557971</v>
+        <v>557990</v>
       </c>
       <c r="R9" t="n">
-        <v>6430606</v>
+        <v>6430595</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1530,54 +1531,57 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136076792</t>
+          <t>https://artportalen.se/Sighting/136076669</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136040303</v>
+        <v>136076792</v>
       </c>
       <c r="B10" t="n">
-        <v>91423</v>
+        <v>92085</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5685</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fredriksdal, Ög</t>
+          <t>Fredriksdal/Björkern, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558113</v>
+        <v>557971</v>
       </c>
       <c r="R10" t="n">
-        <v>6430749</v>
+        <v>6430606</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1615,33 +1619,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136040303</t>
+          <t>https://artportalen.se/Sighting/136076792</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136043436</v>
+        <v>136040303</v>
       </c>
       <c r="B11" t="n">
-        <v>92742</v>
+        <v>91423</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,21 +1654,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6031</v>
+        <v>5685</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557923</v>
+        <v>558113</v>
       </c>
       <c r="R11" t="n">
-        <v>6430664</v>
+        <v>6430749</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,38 +1739,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136043436</t>
+          <t>https://artportalen.se/Sighting/136040303</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136043265</v>
+        <v>136043436</v>
       </c>
       <c r="B12" t="n">
-        <v>80062</v>
+        <v>92742</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557852</v>
+        <v>557923</v>
       </c>
       <c r="R12" t="n">
-        <v>6430699</v>
+        <v>6430664</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,16 +1841,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136043265</t>
+          <t>https://artportalen.se/Sighting/136043436</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136076459</v>
+        <v>136043265</v>
       </c>
       <c r="B13" t="n">
-        <v>57995</v>
+        <v>80062</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1853,45 +1858,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100048</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fredriksdal/Björkern, Ög</t>
+          <t>Fredriksdal, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558122</v>
+        <v>557852</v>
       </c>
       <c r="R13" t="n">
-        <v>6430663</v>
+        <v>6430699</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1923,16 +1920,11 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Bohål i gammal asp</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="b">
         <v>0</v>
@@ -1940,44 +1932,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Madeleine Askelöf</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Madeleine Askelöf</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136076459</t>
+          <t>https://artportalen.se/Sighting/136043265</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136040736</v>
+        <v>136076459</v>
       </c>
       <c r="B14" t="n">
-        <v>57979</v>
+        <v>57995</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1990,23 +1982,23 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fredriksdal, Ög</t>
+          <t>Fredriksdal/Björkern, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558078</v>
+        <v>558122</v>
       </c>
       <c r="R14" t="n">
-        <v>6430683</v>
+        <v>6430663</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2038,11 +2030,16 @@
           <t>2026-08-21</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Bohål i gammal asp</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="b">
         <v>0</v>
@@ -2050,24 +2047,24 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136040736</t>
+          <t>https://artportalen.se/Sighting/136076459</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136043716</v>
+        <v>136040736</v>
       </c>
       <c r="B15" t="n">
         <v>57979</v>
@@ -2110,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558046</v>
+        <v>558078</v>
       </c>
       <c r="R15" t="n">
-        <v>6430557</v>
+        <v>6430683</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2171,13 +2168,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136043716</t>
+          <t>https://artportalen.se/Sighting/136040736</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136076464</v>
+        <v>136043716</v>
       </c>
       <c r="B16" t="n">
         <v>57979</v>
@@ -2210,23 +2207,23 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fredriksdal/Björkern, Ög</t>
+          <t>Fredriksdal, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558122</v>
+        <v>558046</v>
       </c>
       <c r="R16" t="n">
-        <v>6430663</v>
+        <v>6430557</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2258,16 +2255,11 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Bohål i gammal asp</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="b">
         <v>0</v>
@@ -2275,24 +2267,24 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Madeleine Askelöf</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Madeleine Askelöf</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136076464</t>
+          <t>https://artportalen.se/Sighting/136043716</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136076632</v>
+        <v>136076464</v>
       </c>
       <c r="B17" t="n">
         <v>57979</v>
@@ -2325,20 +2317,20 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fredriskdal/Björkern, Ög</t>
+          <t>Fredriksdal/Björkern, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558056</v>
+        <v>558122</v>
       </c>
       <c r="R17" t="n">
-        <v>6430532</v>
+        <v>6430663</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2375,14 +2367,14 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Gamla hackspår på flera döda tallar. Fågeln hörts en bit bort.</t>
+          <t>Bohål i gammal asp</t>
         </is>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG17" t="b">
         <v>0</v>
@@ -2401,13 +2393,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136076632</t>
+          <t>https://artportalen.se/Sighting/136076464</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136076737</v>
+        <v>136076632</v>
       </c>
       <c r="B18" t="n">
         <v>57979</v>
@@ -2446,14 +2438,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fredriksdal/Björkern, Ög</t>
+          <t>Fredriskdal/Björkern, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558001</v>
+        <v>558056</v>
       </c>
       <c r="R18" t="n">
-        <v>6430557</v>
+        <v>6430532</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2490,7 +2482,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Hackspår från födosök på tall</t>
+          <t>Gamla hackspår på flera döda tallar. Fågeln hörts en bit bort.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2516,13 +2508,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136076737</t>
+          <t>https://artportalen.se/Sighting/136076632</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136076810</v>
+        <v>136076737</v>
       </c>
       <c r="B19" t="n">
         <v>57979</v>
@@ -2555,7 +2547,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2565,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557982</v>
+        <v>558001</v>
       </c>
       <c r="R19" t="n">
-        <v>6430645</v>
+        <v>6430557</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2605,7 +2597,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Gammalt, dött träd med sju bohål i spillkråkestorlek.</t>
+          <t>Hackspår från födosök på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2631,63 +2623,62 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136076810</t>
+          <t>https://artportalen.se/Sighting/136076737</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136042346</v>
+        <v>136076810</v>
       </c>
       <c r="B20" t="n">
-        <v>5498</v>
+        <v>57979</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>101410</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fredriksdal, Ög</t>
+          <t>Fredriksdal/Björkern, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557998</v>
+        <v>557982</v>
       </c>
       <c r="R20" t="n">
-        <v>6430568</v>
+        <v>6430645</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2719,37 +2710,41 @@
           <t>2026-08-21</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gammalt, dött träd med sju bohål i spillkråkestorlek.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136042346</t>
+          <t>https://artportalen.se/Sighting/136076810</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136076515</v>
+        <v>136042346</v>
       </c>
       <c r="B21" t="n">
         <v>5498</v>
@@ -2781,21 +2776,25 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fredriksdal/Björkern, Ög</t>
+          <t>Fredriksdal, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558085</v>
+        <v>557998</v>
       </c>
       <c r="R21" t="n">
-        <v>6430572</v>
+        <v>6430568</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2840,24 +2839,24 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Madeleine Askelöf</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Madeleine Askelöf</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136076515</t>
+          <t>https://artportalen.se/Sighting/136042346</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136076717</v>
+        <v>136076515</v>
       </c>
       <c r="B22" t="n">
         <v>5498</v>
@@ -2897,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558001</v>
+        <v>558085</v>
       </c>
       <c r="R22" t="n">
-        <v>6430557</v>
+        <v>6430572</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2959,16 +2958,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136076717</t>
+          <t>https://artportalen.se/Sighting/136076515</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136076901</v>
+        <v>136076717</v>
       </c>
       <c r="B23" t="n">
-        <v>58143</v>
+        <v>5498</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2976,35 +2975,28 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>101410</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3012,13 +3004,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>557944</v>
+        <v>558001</v>
       </c>
       <c r="R23" t="n">
-        <v>6430672</v>
+        <v>6430557</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3050,17 +3042,13 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Hört ihållande sång från tre individer på flera ställen i närheten,</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3078,43 +3066,43 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136076901</t>
+          <t>https://artportalen.se/Sighting/136076717</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136076908</v>
+        <v>136076901</v>
       </c>
       <c r="B24" t="n">
-        <v>58138</v>
+        <v>58143</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -3127,14 +3115,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>fred, Ög</t>
+          <t>Fredriksdal/Björkern, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>557941</v>
+        <v>557944</v>
       </c>
       <c r="R24" t="n">
-        <v>6430693</v>
+        <v>6430672</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3171,7 +3159,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Hört ihållande sång från minst två individer på flera ställen i närheten,</t>
+          <t>Hört ihållande sång från tre individer på flera ställen i närheten,</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3197,33 +3185,33 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136076908</t>
+          <t>https://artportalen.se/Sighting/136076901</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136076497</v>
+        <v>136076908</v>
       </c>
       <c r="B25" t="n">
-        <v>61538</v>
+        <v>58138</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106670</v>
+        <v>103023</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Arion ater ater</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3233,27 +3221,30 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fredriksdal/Björkern, Ög</t>
+          <t>fred, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558073</v>
+        <v>557941</v>
       </c>
       <c r="R25" t="n">
-        <v>6430626</v>
+        <v>6430693</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3285,13 +3276,17 @@
           <t>2026-08-21</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Hört ihållande sång från minst två individer på flera ställen i närheten,</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3309,16 +3304,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136076497</t>
+          <t>https://artportalen.se/Sighting/136076908</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136076819</v>
+        <v>136076497</v>
       </c>
       <c r="B26" t="n">
-        <v>56713</v>
+        <v>61538</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3326,16 +3321,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>206046</v>
+        <v>106670</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Arion ater ater</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3343,14 +3338,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3358,10 +3354,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557973</v>
+        <v>558073</v>
       </c>
       <c r="R26" t="n">
-        <v>6430659</v>
+        <v>6430626</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3402,6 +3398,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3419,54 +3416,62 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136076819</t>
+          <t>https://artportalen.se/Sighting/136076497</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136043932</v>
+        <v>136076819</v>
       </c>
       <c r="B27" t="n">
-        <v>58846</v>
+        <v>56713</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>208249</v>
+        <v>206046</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Fredriksdal, Ög</t>
+          <t>Fredriksdal/Björkern, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558092</v>
+        <v>557973</v>
       </c>
       <c r="R27" t="n">
-        <v>6430618</v>
+        <v>6430659</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3510,70 +3515,62 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136043932</t>
+          <t>https://artportalen.se/Sighting/136076819</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135468428</v>
+        <v>136043932</v>
       </c>
       <c r="B28" t="n">
-        <v>99293</v>
+        <v>58846</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fredriksdal, Fredriksdal, Ög</t>
+          <t>Fredriksdal, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558081</v>
+        <v>558092</v>
       </c>
       <c r="R28" t="n">
-        <v>6430682</v>
+        <v>6430618</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3600,27 +3597,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:21</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>1 blommande, 10 bladrosetter</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3629,31 +3611,30 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linnea Druid</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linnea Druid, Henrik Druid</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135468428</t>
+          <t>https://artportalen.se/Sighting/136043932</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136043853</v>
+        <v>135468428</v>
       </c>
       <c r="B29" t="n">
         <v>99293</v>
@@ -3683,24 +3664,23 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fredriksdal, Ög</t>
+          <t>Fredriksdal, Fredriksdal, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
         <v>558081</v>
       </c>
       <c r="R29" t="n">
-        <v>6430606</v>
+        <v>6430682</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3727,12 +3707,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>1 blommande, 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3741,22 +3736,134 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Linnea Druid</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Linnea Druid, Henrik Druid</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135468428</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136043853</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Fredriksdal, Ög</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>558081</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6430606</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Oppeby</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136043853</t>
         </is>
@@ -3792,6 +3899,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30320-2026 artfynd.xlsx
+++ b/artfynd/A 30320-2026 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>136104297</v>
       </c>
       <c r="B4" t="n">
-        <v>96878</v>
+        <v>96879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136040191</v>
       </c>
       <c r="B5" t="n">
-        <v>96596</v>
+        <v>96597</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136040349</v>
       </c>
       <c r="B6" t="n">
-        <v>92278</v>
+        <v>92279</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>136042696</v>
       </c>
       <c r="B7" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>136043472</v>
       </c>
       <c r="B8" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136076669</v>
       </c>
       <c r="B9" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>136076792</v>
       </c>
       <c r="B10" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136040303</v>
       </c>
       <c r="B11" t="n">
-        <v>91423</v>
+        <v>91424</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136043436</v>
       </c>
       <c r="B12" t="n">
-        <v>92742</v>
+        <v>92743</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>136043265</v>
       </c>
       <c r="B13" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>136043853</v>
       </c>
       <c r="B30" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 30320-2026 artfynd.xlsx
+++ b/artfynd/A 30320-2026 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>136104297</v>
       </c>
       <c r="B4" t="n">
-        <v>96879</v>
+        <v>96880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136040191</v>
       </c>
       <c r="B5" t="n">
-        <v>96597</v>
+        <v>96598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136040349</v>
       </c>
       <c r="B6" t="n">
-        <v>92279</v>
+        <v>92280</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>136042696</v>
       </c>
       <c r="B7" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>136043472</v>
       </c>
       <c r="B8" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136076669</v>
       </c>
       <c r="B9" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>136076792</v>
       </c>
       <c r="B10" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136040303</v>
       </c>
       <c r="B11" t="n">
-        <v>91424</v>
+        <v>91425</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136043436</v>
       </c>
       <c r="B12" t="n">
-        <v>92743</v>
+        <v>92744</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>136043853</v>
       </c>
       <c r="B30" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 30320-2026 artfynd.xlsx
+++ b/artfynd/A 30320-2026 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>136104297</v>
       </c>
       <c r="B4" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136040191</v>
       </c>
       <c r="B5" t="n">
-        <v>96598</v>
+        <v>96599</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136040349</v>
       </c>
       <c r="B6" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>136042696</v>
       </c>
       <c r="B7" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>136043472</v>
       </c>
       <c r="B8" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136076669</v>
       </c>
       <c r="B9" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>136076792</v>
       </c>
       <c r="B10" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136040303</v>
       </c>
       <c r="B11" t="n">
-        <v>91425</v>
+        <v>91426</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136043436</v>
       </c>
       <c r="B12" t="n">
-        <v>92744</v>
+        <v>92745</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>136043265</v>
       </c>
       <c r="B13" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>136076459</v>
       </c>
       <c r="B14" t="n">
-        <v>57995</v>
+        <v>57996</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>136040736</v>
       </c>
       <c r="B15" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136043716</v>
       </c>
       <c r="B16" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>136076464</v>
       </c>
       <c r="B17" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>136076632</v>
       </c>
       <c r="B18" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136076737</v>
       </c>
       <c r="B19" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>136076810</v>
       </c>
       <c r="B20" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>136076901</v>
       </c>
       <c r="B24" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>136076908</v>
       </c>
       <c r="B25" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>136076497</v>
       </c>
       <c r="B26" t="n">
-        <v>61538</v>
+        <v>61539</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>136076819</v>
       </c>
       <c r="B27" t="n">
-        <v>56713</v>
+        <v>56714</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>136043932</v>
       </c>
       <c r="B28" t="n">
-        <v>58846</v>
+        <v>58847</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>136043853</v>
       </c>
       <c r="B30" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 30320-2026 artfynd.xlsx
+++ b/artfynd/A 30320-2026 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>136104297</v>
       </c>
       <c r="B4" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136040191</v>
       </c>
       <c r="B5" t="n">
-        <v>96599</v>
+        <v>96605</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136040349</v>
       </c>
       <c r="B6" t="n">
-        <v>92281</v>
+        <v>92287</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>136042696</v>
       </c>
       <c r="B7" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>136043472</v>
       </c>
       <c r="B8" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136076669</v>
       </c>
       <c r="B9" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>136076792</v>
       </c>
       <c r="B10" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136040303</v>
       </c>
       <c r="B11" t="n">
-        <v>91426</v>
+        <v>91432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136043436</v>
       </c>
       <c r="B12" t="n">
-        <v>92745</v>
+        <v>92751</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>136043265</v>
       </c>
       <c r="B13" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>136076459</v>
       </c>
       <c r="B14" t="n">
-        <v>57996</v>
+        <v>58000</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>136040736</v>
       </c>
       <c r="B15" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136043716</v>
       </c>
       <c r="B16" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>136076464</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>136076632</v>
       </c>
       <c r="B18" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136076737</v>
       </c>
       <c r="B19" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>136076810</v>
       </c>
       <c r="B20" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>136076901</v>
       </c>
       <c r="B24" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>136076908</v>
       </c>
       <c r="B25" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>136076497</v>
       </c>
       <c r="B26" t="n">
-        <v>61539</v>
+        <v>61543</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>136076819</v>
       </c>
       <c r="B27" t="n">
-        <v>56714</v>
+        <v>56718</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>136043932</v>
       </c>
       <c r="B28" t="n">
-        <v>58847</v>
+        <v>58851</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>136043853</v>
       </c>
       <c r="B30" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 30320-2026 artfynd.xlsx
+++ b/artfynd/A 30320-2026 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>136104297</v>
       </c>
       <c r="B4" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136040191</v>
       </c>
       <c r="B5" t="n">
-        <v>96605</v>
+        <v>96606</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136040349</v>
       </c>
       <c r="B6" t="n">
-        <v>92287</v>
+        <v>92288</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>136042696</v>
       </c>
       <c r="B7" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>136043472</v>
       </c>
       <c r="B8" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136076669</v>
       </c>
       <c r="B9" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>136076792</v>
       </c>
       <c r="B10" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136040303</v>
       </c>
       <c r="B11" t="n">
-        <v>91432</v>
+        <v>91433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136043436</v>
       </c>
       <c r="B12" t="n">
-        <v>92751</v>
+        <v>92752</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>136043265</v>
       </c>
       <c r="B13" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>136076459</v>
       </c>
       <c r="B14" t="n">
-        <v>58000</v>
+        <v>58001</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>136040736</v>
       </c>
       <c r="B15" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136043716</v>
       </c>
       <c r="B16" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>136076464</v>
       </c>
       <c r="B17" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>136076632</v>
       </c>
       <c r="B18" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136076737</v>
       </c>
       <c r="B19" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>136076810</v>
       </c>
       <c r="B20" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>136076901</v>
       </c>
       <c r="B24" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>136076908</v>
       </c>
       <c r="B25" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>136076497</v>
       </c>
       <c r="B26" t="n">
-        <v>61543</v>
+        <v>61544</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>136076819</v>
       </c>
       <c r="B27" t="n">
-        <v>56718</v>
+        <v>56719</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>136043932</v>
       </c>
       <c r="B28" t="n">
-        <v>58851</v>
+        <v>58852</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>136043853</v>
       </c>
       <c r="B30" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 30320-2026 artfynd.xlsx
+++ b/artfynd/A 30320-2026 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>136104297</v>
       </c>
       <c r="B4" t="n">
-        <v>96888</v>
+        <v>96899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136040191</v>
       </c>
       <c r="B5" t="n">
-        <v>96606</v>
+        <v>96617</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136040349</v>
       </c>
       <c r="B6" t="n">
-        <v>92288</v>
+        <v>92294</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>136042696</v>
       </c>
       <c r="B7" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>136043472</v>
       </c>
       <c r="B8" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136076669</v>
       </c>
       <c r="B9" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>136076792</v>
       </c>
       <c r="B10" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136040303</v>
       </c>
       <c r="B11" t="n">
-        <v>91433</v>
+        <v>91439</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136043436</v>
       </c>
       <c r="B12" t="n">
-        <v>92752</v>
+        <v>92758</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>136043265</v>
       </c>
       <c r="B13" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>136043853</v>
       </c>
       <c r="B30" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 30320-2026 artfynd.xlsx
+++ b/artfynd/A 30320-2026 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>136104297</v>
       </c>
       <c r="B4" t="n">
-        <v>96899</v>
+        <v>96912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136040191</v>
       </c>
       <c r="B5" t="n">
-        <v>96617</v>
+        <v>96630</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136040349</v>
       </c>
       <c r="B6" t="n">
-        <v>92294</v>
+        <v>92301</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>136042696</v>
       </c>
       <c r="B7" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>136043472</v>
       </c>
       <c r="B8" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136076669</v>
       </c>
       <c r="B9" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>136076792</v>
       </c>
       <c r="B10" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136040303</v>
       </c>
       <c r="B11" t="n">
-        <v>91439</v>
+        <v>91446</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136043436</v>
       </c>
       <c r="B12" t="n">
-        <v>92758</v>
+        <v>92765</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>136043265</v>
       </c>
       <c r="B13" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>136076459</v>
       </c>
       <c r="B14" t="n">
-        <v>58001</v>
+        <v>58006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>136040736</v>
       </c>
       <c r="B15" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136043716</v>
       </c>
       <c r="B16" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>136076464</v>
       </c>
       <c r="B17" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>136076632</v>
       </c>
       <c r="B18" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136076737</v>
       </c>
       <c r="B19" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>136076810</v>
       </c>
       <c r="B20" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>136076901</v>
       </c>
       <c r="B24" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>136076908</v>
       </c>
       <c r="B25" t="n">
-        <v>58144</v>
+        <v>58149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>136076497</v>
       </c>
       <c r="B26" t="n">
-        <v>61544</v>
+        <v>61549</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>136076819</v>
       </c>
       <c r="B27" t="n">
-        <v>56719</v>
+        <v>56724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>136043932</v>
       </c>
       <c r="B28" t="n">
-        <v>58852</v>
+        <v>58857</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>136043853</v>
       </c>
       <c r="B30" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 30320-2026 artfynd.xlsx
+++ b/artfynd/A 30320-2026 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>136104297</v>
       </c>
       <c r="B4" t="n">
-        <v>96912</v>
+        <v>96913</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136040191</v>
       </c>
       <c r="B5" t="n">
-        <v>96630</v>
+        <v>96631</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136040349</v>
       </c>
       <c r="B6" t="n">
-        <v>92301</v>
+        <v>92302</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>136042696</v>
       </c>
       <c r="B7" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>136043472</v>
       </c>
       <c r="B8" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136076669</v>
       </c>
       <c r="B9" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>136076792</v>
       </c>
       <c r="B10" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136040303</v>
       </c>
       <c r="B11" t="n">
-        <v>91446</v>
+        <v>91447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136043436</v>
       </c>
       <c r="B12" t="n">
-        <v>92765</v>
+        <v>92766</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>136043853</v>
       </c>
       <c r="B30" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 30320-2026 artfynd.xlsx
+++ b/artfynd/A 30320-2026 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>136104297</v>
       </c>
       <c r="B4" t="n">
-        <v>96913</v>
+        <v>96926</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136040191</v>
       </c>
       <c r="B5" t="n">
-        <v>96631</v>
+        <v>96644</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136040349</v>
       </c>
       <c r="B6" t="n">
-        <v>92302</v>
+        <v>92315</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>136042696</v>
       </c>
       <c r="B7" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>136043472</v>
       </c>
       <c r="B8" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136076669</v>
       </c>
       <c r="B9" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>136076792</v>
       </c>
       <c r="B10" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136040303</v>
       </c>
       <c r="B11" t="n">
-        <v>91447</v>
+        <v>91460</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136043436</v>
       </c>
       <c r="B12" t="n">
-        <v>92766</v>
+        <v>92779</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>136043265</v>
       </c>
       <c r="B13" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>136076459</v>
       </c>
       <c r="B14" t="n">
-        <v>58006</v>
+        <v>58019</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>136040736</v>
       </c>
       <c r="B15" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136043716</v>
       </c>
       <c r="B16" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>136076464</v>
       </c>
       <c r="B17" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>136076632</v>
       </c>
       <c r="B18" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136076737</v>
       </c>
       <c r="B19" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>136076810</v>
       </c>
       <c r="B20" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>136076901</v>
       </c>
       <c r="B24" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>136076908</v>
       </c>
       <c r="B25" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>136076497</v>
       </c>
       <c r="B26" t="n">
-        <v>61549</v>
+        <v>61562</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>136076819</v>
       </c>
       <c r="B27" t="n">
-        <v>56724</v>
+        <v>56737</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>136043932</v>
       </c>
       <c r="B28" t="n">
-        <v>58857</v>
+        <v>58870</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>136043853</v>
       </c>
       <c r="B30" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 30320-2026 artfynd.xlsx
+++ b/artfynd/A 30320-2026 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>136104297</v>
       </c>
       <c r="B4" t="n">
-        <v>96926</v>
+        <v>96927</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136040191</v>
       </c>
       <c r="B5" t="n">
-        <v>96644</v>
+        <v>96645</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>136040349</v>
       </c>
       <c r="B6" t="n">
-        <v>92315</v>
+        <v>92316</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>136042696</v>
       </c>
       <c r="B7" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>136043472</v>
       </c>
       <c r="B8" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>136076669</v>
       </c>
       <c r="B9" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>136076792</v>
       </c>
       <c r="B10" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136040303</v>
       </c>
       <c r="B11" t="n">
-        <v>91460</v>
+        <v>91461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136043436</v>
       </c>
       <c r="B12" t="n">
-        <v>92779</v>
+        <v>92780</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>136043265</v>
       </c>
       <c r="B13" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>136043853</v>
       </c>
       <c r="B30" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
